--- a/Employee_Reports_wi52/James Kariungi Muthee Q0525.xlsx
+++ b/Employee_Reports_wi52/James Kariungi Muthee Q0525.xlsx
@@ -578,11 +578,11 @@
         </is>
       </c>
       <c r="H3" s="3" t="n">
-        <v>699</v>
+        <v>691</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -627,11 +627,11 @@
         </is>
       </c>
       <c r="H4" s="3" t="n">
-        <v>699</v>
+        <v>691</v>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -676,11 +676,11 @@
         </is>
       </c>
       <c r="H5" s="3" t="n">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -725,11 +725,11 @@
         </is>
       </c>
       <c r="H6" s="3" t="n">
-        <v>701</v>
+        <v>693</v>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
@@ -774,11 +774,11 @@
         </is>
       </c>
       <c r="H7" s="3" t="n">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -823,11 +823,11 @@
         </is>
       </c>
       <c r="H8" s="3" t="n">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -872,11 +872,11 @@
         </is>
       </c>
       <c r="H9" s="3" t="n">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -921,11 +921,11 @@
         </is>
       </c>
       <c r="H10" s="3" t="n">
-        <v>165</v>
+        <v>157</v>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -958,11 +958,11 @@
         </is>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-373</v>
+        <v>-381</v>
       </c>
       <c r="I11" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J11" s="4" t="inlineStr">
@@ -1007,11 +1007,11 @@
         </is>
       </c>
       <c r="H12" s="3" t="n">
-        <v>231</v>
+        <v>223</v>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
@@ -1056,11 +1056,11 @@
         </is>
       </c>
       <c r="H13" s="3" t="n">
-        <v>245</v>
+        <v>237</v>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
@@ -1105,11 +1105,11 @@
         </is>
       </c>
       <c r="H14" s="3" t="n">
-        <v>295</v>
+        <v>287</v>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
@@ -1142,11 +1142,11 @@
         </is>
       </c>
       <c r="H15" s="5" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="I15" s="5" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J15" s="5" t="inlineStr">
@@ -1191,11 +1191,11 @@
         </is>
       </c>
       <c r="H16" s="3" t="n">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
@@ -1228,11 +1228,11 @@
         </is>
       </c>
       <c r="H17" s="3" t="n">
-        <v>324</v>
+        <v>316</v>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
